--- a/countries/de/1990-1994.xlsx
+++ b/countries/de/1990-1994.xlsx
@@ -765,6 +765,11 @@
       <c r="O2" t="n">
         <v>1562</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_DE_ECDC_AIDS_ANNUAL</t>
@@ -782,7 +787,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -792,6 +802,11 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -857,7 +872,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -892,30 +907,113 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1991-01-01</t>
+          <t>1990-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1991-01</t>
+          <t>1990-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1784</v>
+        <v>1562</v>
       </c>
       <c r="O3" t="n">
-        <v>1784</v>
+        <v>1562</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -923,7 +1021,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -933,6 +1036,11 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1033,19 +1141,24 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1992-01</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1945</v>
+        <v>1784</v>
       </c>
       <c r="O4" t="n">
-        <v>1945</v>
+        <v>1784</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1064,7 +1177,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1074,6 +1192,11 @@
       </c>
       <c r="AT4" t="n">
         <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1139,7 +1262,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1174,30 +1297,113 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1993-01</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2030</v>
+        <v>1784</v>
       </c>
       <c r="O5" t="n">
-        <v>2030</v>
+        <v>1784</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1205,7 +1411,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1215,6 +1426,11 @@
       </c>
       <c r="AT5" t="n">
         <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1295,17 +1511,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1315,23 +1531,28 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1993-01</t>
+          <t>1992-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2360</v>
+        <v>1945</v>
       </c>
       <c r="O6" t="n">
-        <v>2360</v>
+        <v>1945</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1346,16 +1567,26 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1421,7 +1652,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1456,30 +1687,113 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1994-01-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1994-01</t>
+          <t>1992-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2141</v>
+        <v>1945</v>
       </c>
       <c r="O7" t="n">
-        <v>2141</v>
+        <v>1945</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1487,7 +1801,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1497,6 +1816,11 @@
       </c>
       <c r="AT7" t="n">
         <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1577,17 +1901,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D005</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1597,23 +1921,28 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1994-01-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1994-01</t>
+          <t>1993-01</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2265</v>
+        <v>2030</v>
       </c>
       <c r="O8" t="n">
-        <v>2265</v>
+        <v>2030</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1628,17 +1957,27 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
         </is>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>rki_survstat</t>
@@ -1675,6 +2014,1410 @@
         </is>
       </c>
       <c r="BC8" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1993-01-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1993-01</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2030</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2030</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1993-01-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1993-01</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2360</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2360</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1993-01-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1993-01</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2360</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2360</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1994-01-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1994-01</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2141</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2141</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1994-01-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1994-01</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>2141</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2141</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_AIDS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1994-01-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1994-01</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2265</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2265</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1994-01-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1994-01</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2265</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2265</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_DE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Germany annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_HIV_INFECTION_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
@@ -1806,7 +3549,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -1826,7 +3569,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1836,7 +3579,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
